--- a/data/excel/meeting.xlsx
+++ b/data/excel/meeting.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,40 +761,160 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>中国共产党第七届中央委员会第二次全体会议</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>七届二中全会</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1949年3月</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全会提出党的工作重心由乡村转移到城市，并告诫全党务必继续保持谦虚谨慎、艰苦奋斗的作风。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>为新中国的成立作了政治上和思想上的准备。</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1949 年 3 月在河北平山西柏坡召开的中共七届二中全会。</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>中国共产党第十八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>中共十八大/十八大</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2012年11月8日</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>大会确立科学发展观为党的指导思想，提出全面建成小康社会的奋斗目标。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>开启了中国特色社会主义新时代。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2012 年 11 月在北京召开的中国共产党第十八次全国代表大会。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>中国共产党第二十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>中共二十大/二十大</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2022年10月16日</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>大会对全面建成社会主义现代化强国、以中国式现代化全面推进中华民族伟大复兴作出战略部署。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>是在全党全国各族人民迈上全面建设社会主义现代化国家新征程的关键时刻召开的一次十分重要的大会。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2022 年 10 月在北京召开的中国共产党第二十次全国代表大会。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>中国社会主义青年团第一次全国代表大会</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>青年团一大</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>1922年5月</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>大会通过团的纲领和章程，正式建立中国社会主义青年团。</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>标志着中国共产党领导的青年组织在全国范围内正式建立。</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>1922 年 5 月在广州召开的中国社会主义青年团第一次全国代表大会。</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>http://cpc.people.com.cn/GB/64162/64168/index.html</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/excel/meeting.xlsx
+++ b/data/excel/meeting.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +918,582 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>中国共产党第二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>中共二大/二大</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1922年7月16日至23日</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>大会第一次提出明确的反帝反封建的民主革命纲领。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1922 年 7 月在上海召开，第一次提出党的民主革命纲领。</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>中国共产党第三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>中共三大/三大</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1923年6月12日至20日</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>大会决定共产党员以个人身份加入国民党，建立革命统一战线。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1923 年 6 月在广州召开，确定国共合作方针。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>中国共产党第四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>中共四大/四大</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1925年1月11日至22日</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>大会提出无产阶级在民主革命中的领导权和工农联盟问题。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1925 年 1 月在上海召开，提出无产阶级领导权问题。</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>中国共产党第五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>中共五大/五大</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1927年4月27日至5月9日</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>大会在大革命危急关头召开，未能解决挽救时局的迫切问题。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1927 年 4 月至 5 月在汉口召开。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>中国共产党第六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中共六大/六大</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1928年6月18日至7月11日</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>大会明确中国社会性质和革命性质，制定了正确的路线和政策。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1928 年 6 月至 7 月在莫斯科近郊召开，是党史上唯一一次在国外召开的全国代表大会。</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>中国共产党第八次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>中共八大/八大</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1956年9月15日至27日</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>大会正确分析国内主要矛盾，提出把党和国家工作重点转移到社会主义建设上来。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1956 年 9 月在北京召开，是新中国成立后党的第一次全国代表大会。</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>中国共产党第九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>中共九大/九大</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1969年4月1日至24日</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>大会在“文化大革命”中召开，使“左”倾错误理论和实践合法化。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1969 年 4 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>中国共产党第十次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>中共十大/十大</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1973年8月24日至28日</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>大会继续了九大的“左”倾错误方针。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1973 年 8 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>中国共产党第十一次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>中共十一大/十一大</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1977年8月12日至18日</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>大会宣告“文化大革命”结束，但仍沿袭了一些错误提法。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1977 年 8 月在北京召开，宣告“文化大革命”结束。</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>中国共产党第十二次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>中共十二大/十二大</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1982年9月1日至11日</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>邓小平在开幕词中提出走自己的道路、建设有中国特色的社会主义。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1982 年 9 月在北京召开，提出建设有中国特色的社会主义。</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>中国共产党第十三次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>中共十三大/十三大</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1987年10月25日至11月1日</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>大会系统阐述社会主义初级阶段理论，确立党的基本路线。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1987 年 10 月至 11 月在北京召开，阐述社会主义初级阶段理论。</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>中国共产党第十四次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>中共十四大/十四大</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1992年10月12日至18日</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>大会明确提出建立社会主义市场经济体制的改革目标。</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1992 年 10 月在北京召开，确立社会主义市场经济体制改革目标。</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>中国共产党第十五次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>中共十五大/十五大</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1997年9月12日至18日</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>大会把邓小平理论确立为党的指导思想并写入党章。</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1997 年 9 月在北京召开，确立邓小平理论为党的指导思想。</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>中国共产党第十六次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>中共十六大/十六大</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2002年11月8日至14日</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>大会把“三个代表”重要思想确立为党的指导思想并写入党章。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2002 年 11 月在北京召开，确立“三个代表”重要思想为党的指导思想。</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>中国共产党第十七次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>中共十七大/十七大</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2007年10月15日至21日</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>大会全面阐述科学发展观的科学内涵与根本要求。</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2007 年 10 月在北京召开，全面阐述科学发展观。</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>中国共产党第十九次全国代表大会</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>中共十九大/十九大</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2017年10月18日至24日</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>大会把习近平新时代中国特色社会主义思想确立为党的指导思想并写入党章。</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2017 年 10 月在北京召开，确立习近平新时代中国特色社会主义思想为党的指导思想。</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.12371.cn/special/lcddh/</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/excel/meeting.xlsx
+++ b/data/excel/meeting.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1491,7 +1491,1519 @@
         </is>
       </c>
       <c r="H29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>通道会议</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1934年12月12日</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>会议讨论红军战略转移方向，多数人赞成毛泽东提出的向贵州进军的主张。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>长征初期中共中央负责人在湖南通道召开的紧急会议。</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>黎平会议</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1934年12月18日</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>会议通过《中央政治局关于战略方针之决定》，肯定毛泽东提出的向贵州转兵的主张。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1934 年 12 月在贵州黎平召开的中央政治局会议，确定了向黔北进军的方针。</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>猴场会议</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1935年1月1日</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>会议重申黎平会议决定，作出《关于渡江后新的行动方针的决定》。</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1935 年元旦在贵州瓮安猴场召开的中央政治局会议。</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>扎西会议</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1935年2月</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>会议讨论中央红军的行动方针与部队整编，通过遵义会议决议大纲。</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1935 年 2 月红军长征途中在云南扎西地区召开的一系列中央政治局会议。</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>苟坝会议</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1935年3月</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>会议决定成立由毛泽东、周恩来、王稼祥组成的三人军事指挥小组。</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1935 年 3 月在贵州遵义苟坝召开的中央政治局会议。</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>两河口会议</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1935年6月26日</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>会议确定红一、红四方面军会师后北上建立川陕甘根据地的战略方针。</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1935 年 6 月红一、红四方面军会师后在四川懋功两河口召开的中央政治局会议。</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>沙窝会议</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1935年8月</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>会议重申北上方针，讨论组织问题。</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1935 年 8 月在四川松潘沙窝召开的中央政治局会议。</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>俄界会议</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1935年9月12日</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>会议作出《关于张国焘同志的错误的决定》，决定率红一方面军主力先行北上。</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1935 年 9 月在甘肃迭部俄界召开的中央政治局扩大会议。</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>榜罗镇会议</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1935年9月27日</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>会议正式决定把红军长征的落脚点放在陕北。</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1935 年 9 月在甘肃通渭榜罗镇召开的中央政治局常委会议。</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>延安文艺座谈会</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1942年5月2日至23日</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>毛泽东在会上作引言和结论，阐明文艺为人民大众、首先为工农兵服务的方向。</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1942 年 5 月在延安召开的文艺工作座谈会，确立了党的文艺方针。</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>中国共产党第六届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>六届六中全会</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1938年9月29日至11月6日</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>会议批准以毛泽东为代表的中央政治局路线，明确提出马克思主义中国化的任务。</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1938 年秋在延安召开，基本纠正了抗战初期的右倾错误。</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>中国共产党第六届中央委员会第七次全体会议</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>六届七中全会</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1944年5月21日至1945年4月20日</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>会议通过《关于若干历史问题的决议》，为党的七大召开作了充分准备。</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1944 年至 1945 年在延安召开，会期最长的一次中央全会。</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>中国人民政治协商会议第一届全体会议</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>政协一届全体会议/新政协</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1949年9月21日至30日</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>会议通过《中国人民政治协商会议共同纲领》，选举中央人民政府委员会，决定国都、国旗、国歌、纪年。</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1949 年 9 月在北平召开，代行全国人民代表大会职权，宣告新中国即将诞生。</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>第一届全国人民代表大会第一次会议</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>一届全国人大一次会议</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1954年9月15日至28日</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>会议通过《中华人民共和国宪法》，选举产生新的国家领导机构。</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1954 年 9 月在北京召开，标志着人民代表大会制度在全国范围内建立。</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>中国共产党第七届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>七届三中全会</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1950年6月6日至9日</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>会议确定党在国民经济恢复时期的中心任务与战略策略方针。</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1950 年 6 月在北京召开，毛泽东作《不要四面出击》的讲话。</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>中国共产党第八届中央委员会第十一次全体会议</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>八届十一中全会</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1966年8月1日至12日</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>会议通过《关于无产阶级文化大革命的决定》。</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1966 年 8 月在北京召开，「文化大革命」在全国范围内全面发动。</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>中央工作会议（七千人大会）</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>七千人大会</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1962年1月11日至2月7日</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>会议初步总结「大跃进」以来的经验教训，强调发扬民主、健全民主集中制。</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1962 年初在北京召开的扩大的中央工作会议，与会者七千余人。</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>中国共产党第八届中央委员会第九次全体会议</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>八届九中全会</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1961年1月14日至18日</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>会议正式决定对国民经济实行「调整、巩固、充实、提高」的八字方针。</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1961 年 1 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>中央工作会议（1978年）</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1978年11月10日至12月15日</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>会议为十一届三中全会作了充分准备，邓小平作《解放思想，实事求是，团结一致向前看》的讲话。</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1978 年底在北京召开，是十一届三中全会的预备会议。</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>中国共产党第十一届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>十一届六中全会</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1981年6月27日至29日</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>会议通过《关于建国以来党的若干历史问题的决议》，科学评价毛泽东的历史地位。</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1981 年 6 月在北京召开，标志着党在指导思想上的拨乱反正胜利完成。</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>中国共产党第十二届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>十二届三中全会</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1984年10月20日</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于经济体制改革的决定》，提出社会主义经济是公有制基础上的有计划的商品经济。</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1984 年 10 月在北京召开，改革重点由农村转向城市。</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>中国共产党第十三届中央委员会第四次全体会议</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>十三届四中全会</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1989年6月23日至24日</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>会议选举江泽民为中央委员会总书记。</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1989 年 6 月在北京召开，形成以江泽民为核心的中央领导集体。</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>中国共产党第十四届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>十四届三中全会</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1993年11月11日至14日</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于建立社会主义市场经济体制若干问题的决定》。</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1993 年 11 月在北京召开，勾画社会主义市场经济体制的基本框架。</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>中国共产党第十五届中央委员会第五次全体会议</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>十五届五中全会</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2000年10月9日至11日</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>会议通过关于制定国民经济和社会发展第十个五年计划的建议。</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2000 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>中国共产党第十六届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>十六届三中全会</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2003年10月11日至14日</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于完善社会主义市场经济体制若干问题的决定》，提出科学发展观。</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2003 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>中国共产党第十六届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>十六届六中全会</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2006年10月8日至11日</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于构建社会主义和谐社会若干重大问题的决定》。</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2006 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>中国共产党第十七届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>十七届三中全会</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2008年10月9日至12日</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于推进农村改革发展若干重大问题的决定》。</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2008 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>中国共产党第十七届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>十七届六中全会</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2011年10月15日至18日</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于深化文化体制改革、推动社会主义文化大发展大繁荣若干重大问题的决定》。</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2011 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>中国共产党第十八届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>十八届三中全会</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2013年11月9日至12日</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于全面深化改革若干重大问题的决定》，提出使市场在资源配置中起决定性作用。</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2013 年 11 月在北京召开，开启全面深化改革新征程。</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>中国共产党第十八届中央委员会第四次全体会议</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>十八届四中全会</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2014年10月20日至23日</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于全面推进依法治国若干重大问题的决定》。</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2014 年 10 月在北京召开，首次以全面推进依法治国为主题。</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>中国共产党第十八届中央委员会第五次全体会议</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>十八届五中全会</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2015年10月26日至29日</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>会议提出创新、协调、绿色、开放、共享的新发展理念。</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2015 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>中国共产党第十八届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>十八届六中全会</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2016年10月24日至27日</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>会议审议通过《关于新形势下党内政治生活的若干准则》和《中国共产党党内监督条例》。</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2016 年 10 月在北京召开，以全面从严治党为主题。</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>中国共产党第十九届中央委员会第四次全体会议</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>十九届四中全会</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2019年10月28日至31日</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于坚持和完善中国特色社会主义制度、推进国家治理体系和治理能力现代化若干重大问题的决定》。</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2019 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>中国共产党第十九届中央委员会第五次全体会议</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>十九届五中全会</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2020年10月26日至29日</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>会议提出到二〇三五年基本实现社会主义现代化远景目标。</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2020 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>中国共产党第十九届中央委员会第六次全体会议</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>十九届六中全会</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2021年11月8日至11日</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于党的百年奋斗重大成就和历史经验的决议》。</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2021 年 11 月在北京召开，通过党史上第三个历史决议。</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>中国共产党第二十届中央委员会第三次全体会议</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>二十届三中全会</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2024年7月15日至18日</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>会议通过《中共中央关于进一步全面深化改革、推进中国式现代化的决定》。</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2024 年 7 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>庐山会议</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>中共中央政治局扩大会议（庐山）</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1959年7月2日至8月16日</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>会议前期总结“大跃进”以来的经验教训，后期错误地开展了“反右倾”斗争。</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1959 年夏在江西庐山召开的中央政治局扩大会议和八届八中全会。</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>全国科学大会</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1978年3月18日至31日</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>邓小平在开幕式上讲话，重申科学技术是生产力、知识分子是工人阶级的一部分。</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1978 年 3 月在北京召开，迎来“科学的春天”。</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>中央新疆工作座谈会</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2010年5月17日至19日</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>会议确定推进新疆跨越式发展和长治久安的战略部署。</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2010 年 5 月在北京召开的第一次中央新疆工作座谈会。</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>中央扶贫开发工作会议</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2015年11月27日至28日</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>会议对打赢脱贫攻坚战作出全面部署，习近平在会上发表讲话。</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2015 年 11 月在北京召开，吹响脱贫攻坚的冲锋号。</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>中央军委改革工作会议</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2015年11月24日至26日</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>会议对深化国防和军队改革作出部署。</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2015 年 11 月在北京召开，启动新一轮国防和军队改革。</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>全国国有企业党的建设工作会议</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2016年10月10日至11日</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>会议明确坚持党对国有企业的领导是重大政治原则。</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2016 年 10 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>全国高校思想政治工作会议</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2016年12月7日至8日</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>会议强调把思想政治工作贯穿教育教学全过程。</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2016 年 12 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>中央全面依法治国工作会议</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2020年11月16日至17日</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>会议明确习近平法治思想在全面依法治国中的指导地位。</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2020 年 11 月在北京召开。</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.dswxyjy.org.cn/GB/434461/index.html</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/excel/meeting.xlsx
+++ b/data/excel/meeting.xlsx
@@ -1543,7 +1543,11 @@
           <t>会议通过《中央政治局关于战略方针之决定》，肯定毛泽东提出的向贵州转兵的主张。</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>会议肯定了毛泽东的正确主张，是长征以来中央领导层在战略方向上的第一次重要转折。</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>1934 年 12 月在贵州黎平召开的中央政治局会议，确定了向黔北进军的方针。</t>
@@ -1575,7 +1579,11 @@
           <t>会议重申黎平会议决定，作出《关于渡江后新的行动方针的决定》。</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>会议重申黎平会议决定，为遵义会议的召开作了直接准备。</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>1935 年元旦在贵州瓮安猴场召开的中央政治局会议。</t>
@@ -1735,7 +1743,11 @@
           <t>会议作出《关于张国焘同志的错误的决定》，决定率红一方面军主力先行北上。</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>会议维护了北上抗日的正确方针，保证了红军主力继续向陕甘前进。</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>1935 年 9 月在甘肃迭部俄界召开的中央政治局扩大会议。</t>
@@ -1767,7 +1779,11 @@
           <t>会议正式决定把红军长征的落脚点放在陕北。</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>会议确定把长征落脚点放在陕北，为中国革命大本营奠基西北作出决策。</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>1935 年 9 月在甘肃通渭榜罗镇召开的中央政治局常委会议。</t>
@@ -1799,7 +1815,11 @@
           <t>毛泽东在会上作引言和结论，阐明文艺为人民大众、首先为工农兵服务的方向。</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>会议确立了文艺为人民大众、首先为工农兵服务的方向，对此后党的文艺工作影响深远。</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>1942 年 5 月在延安召开的文艺工作座谈会，确立了党的文艺方针。</t>
@@ -1835,7 +1855,11 @@
           <t>会议批准以毛泽东为代表的中央政治局路线，明确提出马克思主义中国化的任务。</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>会议基本纠正了抗战初期的右倾错误，第一次提出马克思主义中国化的任务。</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>1938 年秋在延安召开，基本纠正了抗战初期的右倾错误。</t>
@@ -1871,7 +1895,11 @@
           <t>会议通过《关于若干历史问题的决议》，为党的七大召开作了充分准备。</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>会议通过第一个历史决议，统一了全党对党的历史的认识，为七大作了充分准备。</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>1944 年至 1945 年在延安召开，会期最长的一次中央全会。</t>
@@ -1907,7 +1935,11 @@
           <t>会议通过《中国人民政治协商会议共同纲领》，选举中央人民政府委员会，决定国都、国旗、国歌、纪年。</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>会议通过起临时宪法作用的共同纲领并组建中央人民政府，宣告新中国的诞生。</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>1949 年 9 月在北平召开，代行全国人民代表大会职权，宣告新中国即将诞生。</t>
@@ -1943,7 +1975,11 @@
           <t>会议通过《中华人民共和国宪法》，选举产生新的国家领导机构。</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>会议通过新中国第一部宪法，标志人民代表大会制度在全国范围内建立。</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>1954 年 9 月在北京召开，标志着人民代表大会制度在全国范围内建立。</t>
@@ -1979,7 +2015,11 @@
           <t>会议确定党在国民经济恢复时期的中心任务与战略策略方针。</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>会议确定了国民经济恢复时期的中心任务与策略方针，被称为新中国成立初期的重要战略部署。</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>1950 年 6 月在北京召开，毛泽东作《不要四面出击》的讲话。</t>
@@ -2015,7 +2055,11 @@
           <t>会议通过《关于无产阶级文化大革命的决定》。</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>会议通过“十六条”，使“文化大革命”在全国范围内全面发动。</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>1966 年 8 月在北京召开，「文化大革命」在全国范围内全面发动。</t>
@@ -2051,7 +2095,11 @@
           <t>会议初步总结「大跃进」以来的经验教训，强调发扬民主、健全民主集中制。</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>会议初步总结“大跃进”以来的经验教训，对统一认识、克服困难起了积极作用。</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>1962 年初在北京召开的扩大的中央工作会议，与会者七千余人。</t>
@@ -2087,7 +2135,11 @@
           <t>会议正式决定对国民经济实行「调整、巩固、充实、提高」的八字方针。</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>会议确定“调整、巩固、充实、提高”八字方针，开始全面调整国民经济。</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>1961 年 1 月在北京召开。</t>
@@ -2119,7 +2171,11 @@
           <t>会议为十一届三中全会作了充分准备，邓小平作《解放思想，实事求是，团结一致向前看》的讲话。</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>会议实现了党的思想路线的拨乱反正，为十一届三中全会的召开作了充分准备。</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>1978 年底在北京召开，是十一届三中全会的预备会议。</t>
@@ -2155,7 +2211,11 @@
           <t>会议通过《关于建国以来党的若干历史问题的决议》，科学评价毛泽东的历史地位。</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>会议通过第二个历史决议，科学评价毛泽东的历史地位，标志党在指导思想上的拨乱反正胜利完成。</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>1981 年 6 月在北京召开，标志着党在指导思想上的拨乱反正胜利完成。</t>
@@ -2191,7 +2251,11 @@
           <t>会议通过《中共中央关于经济体制改革的决定》，提出社会主义经济是公有制基础上的有计划的商品经济。</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>会议突破了计划经济与商品经济对立的传统观念，把改革的重点由农村转向城市。</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>1984 年 10 月在北京召开，改革重点由农村转向城市。</t>
@@ -2227,7 +2291,11 @@
           <t>会议选举江泽民为中央委员会总书记。</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>会议形成以江泽民同志为核心的中央领导集体，保证了改革开放事业继续推进。</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>1989 年 6 月在北京召开，形成以江泽民为核心的中央领导集体。</t>
@@ -2263,7 +2331,11 @@
           <t>会议通过《中共中央关于建立社会主义市场经济体制若干问题的决定》。</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>会议勾画出社会主义市场经济体制的基本框架，使改革目标具体化、系统化。</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>1993 年 11 月在北京召开，勾画社会主义市场经济体制的基本框架。</t>
@@ -2335,7 +2407,11 @@
           <t>会议通过《中共中央关于完善社会主义市场经济体制若干问题的决定》，提出科学发展观。</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>会议首次完整提出科学发展观，明确了新世纪新阶段的发展思路。</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>2003 年 10 月在北京召开。</t>
@@ -2479,7 +2555,11 @@
           <t>会议通过《中共中央关于全面深化改革若干重大问题的决定》，提出使市场在资源配置中起决定性作用。</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>会议提出使市场在资源配置中起决定性作用，开启全面深化改革新征程。</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>2013 年 11 月在北京召开，开启全面深化改革新征程。</t>
@@ -2515,7 +2595,11 @@
           <t>会议通过《中共中央关于全面推进依法治国若干重大问题的决定》。</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>会议首次以全面推进依法治国为主题，对建设中国特色社会主义法治体系作出整体部署。</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>2014 年 10 月在北京召开，首次以全面推进依法治国为主题。</t>
@@ -2551,7 +2635,11 @@
           <t>会议提出创新、协调、绿色、开放、共享的新发展理念。</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>会议提出新发展理念，是关系发展全局的一场深刻变革。</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>2015 年 10 月在北京召开。</t>
@@ -2587,7 +2675,11 @@
           <t>会议审议通过《关于新形势下党内政治生活的若干准则》和《中国共产党党内监督条例》。</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>会议以全面从严治党为主题，为新形势下党内政治生活立下规矩。</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>2016 年 10 月在北京召开，以全面从严治党为主题。</t>
@@ -2623,7 +2715,11 @@
           <t>会议通过《中共中央关于坚持和完善中国特色社会主义制度、推进国家治理体系和治理能力现代化若干重大问题的决定》。</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>会议首次系统总结中国特色社会主义制度的显著优势，对推进国家治理现代化作出部署。</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>2019 年 10 月在北京召开。</t>
@@ -2695,7 +2791,11 @@
           <t>会议通过《中共中央关于党的百年奋斗重大成就和历史经验的决议》。</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>会议通过第三个历史决议，系统总结党的百年奋斗重大成就和历史经验。</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>2021 年 11 月在北京召开，通过党史上第三个历史决议。</t>
@@ -2731,7 +2831,11 @@
           <t>会议通过《中共中央关于进一步全面深化改革、推进中国式现代化的决定》。</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>会议对进一步全面深化改革、推进中国式现代化作出系统部署。</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>2024 年 7 月在北京召开。</t>
@@ -2767,7 +2871,11 @@
           <t>会议前期总结“大跃进”以来的经验教训，后期错误地开展了“反右倾”斗争。</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>会议后期错误开展“反右倾”斗争，中断了纠“左”进程，是党的历史上的沉痛教训。</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>1959 年夏在江西庐山召开的中央政治局扩大会议和八届八中全会。</t>
@@ -2799,7 +2907,11 @@
           <t>邓小平在开幕式上讲话，重申科学技术是生产力、知识分子是工人阶级的一部分。</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>会议重申科学技术是生产力、知识分子是工人阶级的一部分，迎来“科学的春天”。</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>1978 年 3 月在北京召开，迎来“科学的春天”。</t>

--- a/data/excel/meeting.xlsx
+++ b/data/excel/meeting.xlsx
@@ -1511,7 +1511,11 @@
           <t>会议讨论红军战略转移方向，多数人赞成毛泽东提出的向贵州进军的主张。</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>长征以来中央领导层在战略方向上的第一次重要转折，为黎平会议改变进军方向作了准备。</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>长征初期中共中央负责人在湖南通道召开的紧急会议。</t>
@@ -1679,7 +1683,11 @@
           <t>会议确定红一、红四方面军会师后北上建立川陕甘根据地的战略方针。</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>确定了红一、红四方面军会师后北上建立川陕甘根据地的战略方针。</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>1935 年 6 月红一、红四方面军会师后在四川懋功两河口召开的中央政治局会议。</t>
